--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
   <si>
     <t>Filename</t>
   </si>
@@ -811,676 +811,694 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9922,0.0016,0.0017,0.0008</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9885,0.0025,0.0035,0.0013</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.0001,0.9999</t>
   </si>
   <si>
-    <t>0.9794,0.0002,0.0000,0.0128</t>
-  </si>
-  <si>
-    <t>0.0978,0.0000,0.0000,0.9852</t>
+    <t>0.9927,0.0002,0.0001,0.0037</t>
+  </si>
+  <si>
+    <t>0.0809,0.0000,0.0000,0.9846</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0028,0.0003,0.0003</t>
+  </si>
+  <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9226,0.0071,0.0421,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.4788,0.0008,0.6029,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0434,0.9582,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9777,0.0007,0.0134,0.0004</t>
+  </si>
+  <si>
+    <t>0.9888,0.0004,0.0057,0.0001</t>
+  </si>
+  <si>
+    <t>0.0035,0.0003,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0013,0.9967,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.0002,0.9972,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.0682,0.9334,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.9248,0.0618,0.0048,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9992,0.0064</t>
+  </si>
+  <si>
+    <t>0.0007,0.9983,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.9729,0.0177,0.0031,0.0011</t>
+  </si>
+  <si>
+    <t>0.9906,0.0046,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.0110,0.9892,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.9949,0.0037,0.0002</t>
+  </si>
+  <si>
+    <t>0.0255,0.6534,0.2073,0.0054</t>
+  </si>
+  <si>
+    <t>0.0006,0.0120,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0016,0.9987,0.0005</t>
+  </si>
+  <si>
+    <t>0.0044,0.0000,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0066,0.7987,0.1270,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9860,0.0001,0.9090</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.2164,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0378,0.0003,0.9640,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0043,0.0008,0.9956,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0009,0.9969,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0015,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0012,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9894,0.0097,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0019,0.9994,0.0005</t>
+  </si>
+  <si>
+    <t>0.9976,0.0006,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9962,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9943,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.9979,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9312,0.0036,0.0726,0.0000</t>
+  </si>
+  <si>
+    <t>0.9859,0.0075,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0031,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.8522,0.9756,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.9273,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9560,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0652,0.9984</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0003,0.9998</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.6396,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9883,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9396,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.3155,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9554,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9930,0.5949,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0021,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0008,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0009,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9948,0.0056,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0016,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0168,0.0006,0.9865,0.0001</t>
+  </si>
+  <si>
+    <t>0.9918,0.0003,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.0073,0.0003,0.9920,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9976,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5113,0.6241,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.4511,0.0027,0.4776,0.0029</t>
+  </si>
+  <si>
+    <t>0.9801,0.0004,0.0188,0.0000</t>
+  </si>
+  <si>
+    <t>0.1344,0.5531,0.0214,0.0103</t>
+  </si>
+  <si>
+    <t>0.2688,0.0023,0.6829,0.0029</t>
+  </si>
+  <si>
+    <t>0.0007,0.0231,0.0007,0.9945</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.3986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.4758,0.4779,0.0184,0.0003</t>
+  </si>
+  <si>
+    <t>0.7965,0.2065,0.0073,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.8326,0.9950,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.6377,0.9598,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0012,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0101,0.0068,0.9786,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8565,0.0330,0.0646,0.0009</t>
+  </si>
+  <si>
+    <t>0.1286,0.0008,0.9065,0.0002</t>
+  </si>
+  <si>
+    <t>0.8244,0.0241,0.0365,0.0036</t>
+  </si>
+  <si>
+    <t>0.0895,0.0000,0.0000,0.9812</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.9856,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0060,0.9901,0.0017,0.0020</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.4083,0.5671,0.0039,0.0011</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0601,0.0000,0.0002,0.9828</t>
+  </si>
+  <si>
+    <t>0.0202,0.0150,0.9748,0.0039</t>
+  </si>
+  <si>
+    <t>0.9771,0.0002,0.0029,0.0091</t>
+  </si>
+  <si>
+    <t>0.9916,0.0019,0.0011,0.0030</t>
+  </si>
+  <si>
+    <t>0.6350,0.3712,0.0045,0.0004</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9733,0.0239,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0408,0.9388,0.0080,0.0003</t>
+  </si>
+  <si>
+    <t>0.5892,0.3446,0.0088,0.0018</t>
+  </si>
+  <si>
+    <t>0.9917,0.0019,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9953,0.0005,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9948,0.0018,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9917,0.0035,0.0006,0.0018</t>
+  </si>
+  <si>
+    <t>0.9970,0.0003,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.0310,0.9673,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.2240,0.8082,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.1710,0.8498,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.3345,0.1093,0.5499,0.0011</t>
+  </si>
+  <si>
+    <t>0.9862,0.0207,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9779,0.0110,0.0071,0.0005</t>
+  </si>
+  <si>
+    <t>0.9978,0.0016,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9040,0.1362,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0005,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.9924,0.0024,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0327,0.9980,0.0044</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9987,0.0007</t>
+  </si>
+  <si>
+    <t>0.0013,0.0066,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.0322,0.9502,0.0026</t>
+  </si>
+  <si>
+    <t>0.0096,0.0036,0.9836,0.0011</t>
+  </si>
+  <si>
+    <t>0.0024,0.0024,0.9921,0.0007</t>
+  </si>
+  <si>
+    <t>0.0492,0.0309,0.8689,0.0004</t>
+  </si>
+  <si>
+    <t>0.0274,0.0761,0.8145,0.0003</t>
+  </si>
+  <si>
+    <t>0.2667,0.0132,0.6584,0.0007</t>
+  </si>
+  <si>
+    <t>0.9693,0.0003,0.0284,0.0002</t>
+  </si>
+  <si>
+    <t>0.1220,0.0026,0.9080,0.0003</t>
+  </si>
+  <si>
+    <t>0.0197,0.9830,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0329,0.9744,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0070,0.9936,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9980,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0015,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9934,0.0003,0.0032,0.0000</t>
+  </si>
+  <si>
+    <t>0.9821,0.0023,0.0043,0.0026</t>
+  </si>
+  <si>
+    <t>0.9843,0.0005,0.0086,0.0002</t>
+  </si>
+  <si>
+    <t>0.9665,0.0002,0.0236,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9993,0.0028</t>
+  </si>
+  <si>
+    <t>0.0018,0.0173,0.9949,0.0004</t>
+  </si>
+  <si>
+    <t>0.0077,0.0991,0.9299,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0049,0.9940,0.0008</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9971,0.0010,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9949,0.0017,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9992,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0029,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0042,0.9994,0.0011</t>
+  </si>
+  <si>
+    <t>0.0171,0.5533,0.2964,0.0072</t>
+  </si>
+  <si>
+    <t>0.9970,0.0002,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0020,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0422,0.9775,0.0006</t>
+  </si>
+  <si>
+    <t>0.0143,0.0018,0.9807,0.0003</t>
+  </si>
+  <si>
+    <t>0.0042,0.0000,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0006,0.9978,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.1444,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.9750,0.0005,0.0180,0.0003</t>
+  </si>
+  <si>
+    <t>0.1540,0.0013,0.8723,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0011,0.0000</t>
+  </si>
+  <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9984,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0036,0.0007,0.0002</t>
+  </si>
+  <si>
     <t>0.9995,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9982,0.0007,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9612,0.0011,0.0356,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.0031,0.9908,0.0007</t>
-  </si>
-  <si>
-    <t>0.9833,0.0006,0.0126,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.1168,0.8915,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9922,0.0001,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.7470,0.0015,0.2751,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.0038,0.9940,0.0005</t>
-  </si>
-  <si>
-    <t>0.0147,0.0027,0.9744,0.0016</t>
-  </si>
-  <si>
-    <t>0.0108,0.0002,0.9907,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9991,0.0024</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0534,0.9400,0.0031,0.0004</t>
-  </si>
-  <si>
-    <t>0.9839,0.0183,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.9987,0.0026</t>
-  </si>
-  <si>
-    <t>0.0018,0.9955,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.9897,0.0054,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9982,0.0005,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0303,0.9753,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.9866,0.0133,0.0007</t>
-  </si>
-  <si>
-    <t>0.0144,0.8635,0.1033,0.0048</t>
-  </si>
-  <si>
-    <t>0.0015,0.0007,0.9958,0.0011</t>
-  </si>
-  <si>
-    <t>0.0016,0.0007,0.9957,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.9978,0.0003</t>
-  </si>
-  <si>
-    <t>0.0021,0.0013,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.0147,0.8344,0.0780,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0034,0.8827,0.0003,0.6163</t>
-  </si>
-  <si>
-    <t>0.0004,0.9993,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0176,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0003,0.9970,0.0005</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0033,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0014,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0042,0.9987,0.0004</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.9606,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.9933,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9528,0.0140,0.0190,0.0001</t>
-  </si>
-  <si>
-    <t>0.4853,0.2554,0.1067,0.0011</t>
-  </si>
-  <si>
-    <t>0.0001,0.0044,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9766,0.9891,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9611,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9850,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9705,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0316,0.9982</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0002,0.9998</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.7823,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9914,0.8013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3097,0.9968,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9066,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.3882,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9850,0.0243,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9835,0.0264,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0193,0.0061,0.9801,0.0004</t>
-  </si>
-  <si>
-    <t>0.9966,0.0001,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9973,0.0028,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.9955,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.6840,0.4321,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.4043,0.0051,0.5484,0.0020</t>
-  </si>
-  <si>
-    <t>0.9824,0.0018,0.0069,0.0003</t>
-  </si>
-  <si>
-    <t>0.0984,0.5795,0.0475,0.0083</t>
-  </si>
-  <si>
-    <t>0.9566,0.0026,0.0211,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.0444,0.0004,0.9967</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0088,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.2466,0.7956,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.5089,0.4823,0.0088,0.0007</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0005,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9624,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3468,0.9908,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0018,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0669,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.9919,0.0015,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.6369,0.0002,0.4226,0.0002</t>
-  </si>
-  <si>
-    <t>0.9274,0.0058,0.0250,0.0022</t>
-  </si>
-  <si>
-    <t>0.0402,0.0000,0.0000,0.9921</t>
-  </si>
-  <si>
-    <t>0.0000,0.0022,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9945,0.9820,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0029,0.9946,0.0010,0.0020</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.1117,0.8748,0.0053,0.0010</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.0000,0.0007,0.9985</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.1285,0.0231,0.8854,0.0015</t>
-  </si>
-  <si>
-    <t>0.6252,0.0000,0.0064,0.2101</t>
-  </si>
-  <si>
-    <t>0.9901,0.0005,0.0003,0.0075</t>
-  </si>
-  <si>
-    <t>0.5321,0.5323,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9951,0.0031,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.5592,0.3395,0.0179,0.0006</t>
-  </si>
-  <si>
-    <t>0.1176,0.0660,0.6840,0.0009</t>
-  </si>
-  <si>
-    <t>0.9803,0.0085,0.0016,0.0011</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9979,0.0005,0.0006,0.0004</t>
-  </si>
-  <si>
     <t>0.9992,0.0002,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9989,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0014,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.4027,0.5815,0.0023,0.0009</t>
-  </si>
-  <si>
-    <t>0.1888,0.8072,0.0056,0.0002</t>
-  </si>
-  <si>
-    <t>0.5784,0.4614,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.0137,0.3800,0.9285,0.0010</t>
-  </si>
-  <si>
-    <t>0.9861,0.0176,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0009,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0008,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.5323,0.6132,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0010,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.9750,0.0113,0.0068,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0015,0.9982,0.0029</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9987,0.0003</t>
-  </si>
-  <si>
-    <t>0.0112,0.0024,0.9903,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0046,0.0189,0.9544,0.0015</t>
-  </si>
-  <si>
-    <t>0.0077,0.0017,0.9910,0.0002</t>
-  </si>
-  <si>
-    <t>0.0925,0.0040,0.8835,0.0012</t>
-  </si>
-  <si>
-    <t>0.2212,0.0164,0.6945,0.0002</t>
-  </si>
-  <si>
-    <t>0.0239,0.0279,0.9191,0.0006</t>
-  </si>
-  <si>
-    <t>0.9533,0.0048,0.0243,0.0002</t>
-  </si>
-  <si>
-    <t>0.9304,0.0050,0.0397,0.0014</t>
-  </si>
-  <si>
-    <t>0.0267,0.0127,0.9467,0.0017</t>
-  </si>
-  <si>
-    <t>0.0031,0.9963,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9987,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.9953,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0510,0.9585,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0229,0.9845,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9923,0.0031,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9774,0.0022,0.0106,0.0006</t>
-  </si>
-  <si>
-    <t>0.7985,0.0255,0.0191,0.0431</t>
-  </si>
-  <si>
-    <t>0.9548,0.0007,0.0398,0.0003</t>
-  </si>
-  <si>
-    <t>0.8755,0.0035,0.1034,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9997,0.0014</t>
-  </si>
-  <si>
-    <t>0.0012,0.3989,0.9762,0.0009</t>
-  </si>
-  <si>
-    <t>0.0057,0.8825,0.3991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0042,0.0022,0.9877,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0168,0.9942,0.0004</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0027,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0085,0.9969,0.0012</t>
-  </si>
-  <si>
-    <t>0.0601,0.8580,0.0371,0.0022</t>
-  </si>
-  <si>
-    <t>0.9961,0.0003,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.1286,0.9862,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.0022,0.9922,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0007,0.9980,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.0538,0.9984,0.0003</t>
-  </si>
-  <si>
-    <t>0.9628,0.0003,0.0387,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0000,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0022,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0026,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9788,0.0244,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0086,0.0051,0.9706,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0097,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0014,0.9974,0.0002</t>
-  </si>
-  <si>
-    <t>0.0076,0.0016,0.9839,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0114,0.0014,0.9832,0.0034</t>
-  </si>
-  <si>
-    <t>0.0708,0.0084,0.8929,0.0043</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.9955,0.0098</t>
-  </si>
-  <si>
-    <t>0.9939,0.0000,0.0003,0.0035</t>
-  </si>
-  <si>
-    <t>0.0012,0.0135,0.0001,0.9984</t>
-  </si>
-  <si>
-    <t>0.0125,0.0002,0.0006,0.9960</t>
-  </si>
-  <si>
-    <t>0.9258,0.0051,0.0036,0.0295</t>
+    <t>0.0093,0.0087,0.9476,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.0021,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0407,0.9774,0.0005</t>
+  </si>
+  <si>
+    <t>0.0056,0.0098,0.9745,0.0009</t>
+  </si>
+  <si>
+    <t>0.0466,0.0025,0.4005,0.1717</t>
+  </si>
+  <si>
+    <t>0.6110,0.0181,0.2584,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.0003,0.9941,0.0085</t>
+  </si>
+  <si>
+    <t>0.9803,0.0000,0.0002,0.0220</t>
+  </si>
+  <si>
+    <t>0.0002,0.0029,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0297,0.0001,0.0005,0.9917</t>
+  </si>
+  <si>
+    <t>0.9687,0.0008,0.0004,0.0142</t>
   </si>
 </sst>
 </file>
@@ -1866,7 +1884,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1880,7 +1898,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1894,7 +1912,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1908,7 +1926,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1922,7 +1940,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1936,7 +1954,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1950,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1964,7 +1982,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1978,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1992,7 +2010,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2006,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2020,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2034,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2048,7 +2066,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2059,10 +2077,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2076,7 +2094,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2090,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2104,7 +2122,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2118,7 +2136,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2132,7 +2150,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2146,7 +2164,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2160,7 +2178,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2174,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2188,7 +2206,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2202,7 +2220,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2216,7 +2234,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2230,7 +2248,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2244,7 +2262,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2258,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2272,7 +2290,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2286,7 +2304,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2300,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2314,7 +2332,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2328,7 +2346,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2342,7 +2360,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2356,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2370,7 +2388,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2384,7 +2402,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2398,7 +2416,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2412,7 +2430,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2426,7 +2444,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2440,7 +2458,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2454,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2468,7 +2486,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2482,7 +2500,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2496,7 +2514,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2510,7 +2528,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2524,7 +2542,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2538,7 +2556,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2552,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2566,7 +2584,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2580,7 +2598,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2594,7 +2612,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2608,7 +2626,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2622,7 +2640,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2636,7 +2654,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2650,7 +2668,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2664,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2678,7 +2696,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2692,7 +2710,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2706,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2720,7 +2738,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2734,7 +2752,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2748,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2762,7 +2780,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2776,7 +2794,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2790,7 +2808,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2804,7 +2822,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2818,7 +2836,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2832,7 +2850,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2846,7 +2864,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2860,7 +2878,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2874,7 +2892,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2888,7 +2906,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2902,7 +2920,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2916,7 +2934,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2930,7 +2948,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2944,7 +2962,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2958,7 +2976,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2972,7 +2990,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2986,7 +3004,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3000,7 +3018,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3014,7 +3032,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3028,7 +3046,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3042,7 +3060,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3056,7 +3074,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3067,10 +3085,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3084,7 +3102,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3098,7 +3116,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3112,7 +3130,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3126,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3140,7 +3158,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>275</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3154,7 +3172,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3196,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>356</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3210,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3252,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3266,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3280,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3294,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3308,7 +3326,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3322,7 +3340,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3336,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3350,7 +3368,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3364,7 +3382,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>361</v>
+        <v>285</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3378,7 +3396,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>363</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3392,7 +3410,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3406,7 +3424,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3420,7 +3438,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>364</v>
+        <v>284</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3434,7 +3452,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>284</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3445,10 +3463,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3459,10 +3477,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3476,7 +3494,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3490,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3501,10 +3519,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3518,7 +3536,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3532,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3546,7 +3564,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>284</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3560,7 +3578,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>284</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3574,7 +3592,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3588,7 +3606,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3599,10 +3617,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3616,7 +3634,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3630,7 +3648,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3644,7 +3662,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3658,7 +3676,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3672,7 +3690,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3686,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>274</v>
+        <v>383</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3700,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3714,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>274</v>
+        <v>385</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3728,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3742,7 +3760,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3753,10 +3771,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3770,7 +3788,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3784,7 +3802,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3798,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>270</v>
+        <v>391</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3812,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3823,10 +3841,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3840,7 +3858,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3854,7 +3872,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3868,7 +3886,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>338</v>
+        <v>396</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3882,7 +3900,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3896,7 +3914,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3910,7 +3928,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3924,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3938,7 +3956,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3952,7 +3970,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3966,7 +3984,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3980,7 +3998,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3994,7 +4012,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4008,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4022,7 +4040,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4036,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4050,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4061,10 +4079,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4078,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4092,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4103,10 +4121,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4117,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4134,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4148,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4162,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4176,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4190,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4204,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>383</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4218,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4232,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4246,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4260,7 +4278,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4274,7 +4292,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4285,10 +4303,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4302,7 +4320,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4316,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4330,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4344,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4355,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4372,7 +4390,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4386,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4400,7 +4418,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4414,7 +4432,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4428,7 +4446,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4442,7 +4460,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4456,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>327</v>
+        <v>434</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4470,7 +4488,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>291</v>
+        <v>359</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4484,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4498,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4512,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4526,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4540,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4554,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4565,10 +4583,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4582,7 +4600,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4596,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4610,7 +4628,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4624,7 +4642,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4638,7 +4656,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4652,7 +4670,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4666,7 +4684,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4680,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4694,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4708,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4722,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4736,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4750,7 +4768,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4764,7 +4782,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4775,10 +4793,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4792,7 +4810,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4806,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4820,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4834,7 +4852,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>354</v>
+        <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4848,7 +4866,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4862,7 +4880,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>350</v>
+        <v>462</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4876,7 +4894,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4890,7 +4908,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4904,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4918,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4932,7 +4950,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4946,7 +4964,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4960,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4974,7 +4992,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>327</v>
+        <v>469</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4988,7 +5006,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5002,7 +5020,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5016,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>464</v>
+        <v>430</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5030,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5044,7 +5062,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5058,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5072,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5086,7 +5104,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5097,10 +5115,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5114,7 +5132,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5128,7 +5146,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5142,7 +5160,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5156,7 +5174,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>474</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5170,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5198,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5212,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>376</v>
+        <v>479</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5226,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>270</v>
+        <v>483</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5240,7 +5258,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5254,7 +5272,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5268,7 +5286,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5282,7 +5300,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5296,7 +5314,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>481</v>
+        <v>326</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5307,10 +5325,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D248" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5321,10 +5339,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5338,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5352,7 +5370,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5366,7 +5384,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5380,7 +5398,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5394,7 +5412,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>338</v>
+        <v>396</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5408,7 +5426,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>338</v>
+        <v>396</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5422,7 +5440,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
